--- a/用卷/xlsx/常规科目/2008.xlsx
+++ b/用卷/xlsx/常规科目/2008.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DD8699-BF01-4ABC-9019-D019B5BC9DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C029129-C36A-4C82-BA3A-E08A6CB0B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,6 +711,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -723,9 +741,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -740,21 +755,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,20 +1041,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1193,10 +1193,10 @@
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="18"/>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -1205,8 +1205,8 @@
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="19"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="24"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -1503,11 +1503,11 @@
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
@@ -1553,51 +1553,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="17">
         <v>13</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="24"/>
-    </row>
-    <row r="46" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="18"/>
+      <c r="C45" s="15"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="24"/>
-    </row>
-    <row r="47" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="18"/>
+      <c r="C46" s="15"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="24"/>
-    </row>
-    <row r="48" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="18"/>
+      <c r="C47" s="15"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="24"/>
-    </row>
-    <row r="49" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="18"/>
+      <c r="C48" s="15"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="25"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="16"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
